--- a/2026IAD220_Jugine_Corpuz_test_output.xlsx
+++ b/2026IAD220_Jugine_Corpuz_test_output.xlsx
@@ -166,7 +166,7 @@
     <t>First Time</t>
   </si>
   <si>
-    <t>During the audit, Ms.</t>
+    <t>During the audit, Ms. Corpuz presented a copy of the request sent via webmail seeking approval for the consolidation of the Petty Cash Fund...</t>
   </si>
   <si>
     <t>Follow-up with HR</t>
